--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -801,12 +801,7 @@
         <v>74480242</v>
       </c>
       <c r="B3" t="n">
-        <v>105698</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496438.8207728</v>
+        <v>496439</v>
       </c>
       <c r="R3" t="n">
-        <v>6430881.165125851</v>
+        <v>6430881</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -871,19 +866,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74480242</v>
       </c>
       <c r="B3" t="n">
-        <v>108150</v>
+        <v>108159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74480242</v>
       </c>
       <c r="B3" t="n">
-        <v>108159</v>
+        <v>108164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74480242</v>
       </c>
       <c r="B3" t="n">
-        <v>108164</v>
+        <v>108192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74480242</v>
       </c>
       <c r="B3" t="n">
-        <v>108192</v>
+        <v>108198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74480242</v>
       </c>
       <c r="B3" t="n">
-        <v>108198</v>
+        <v>108205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51215-2020 artfynd.xlsx
+++ b/artfynd/A 51215-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74480242</v>
       </c>
       <c r="B3" t="n">
-        <v>108205</v>
+        <v>108209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
